--- a/education_surveys/020_student_perception_survey--education_surveys.xlsx
+++ b/education_surveys/020_student_perception_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
